--- a/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS6500C_SW2.xlsx
+++ b/tools/_out/orfs_gen_20261020/out/tee/DesignTable_FS6500C_SW2.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BN3"/>
+  <dimension ref="A1:BM3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -519,225 +519,220 @@
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>FSW2_CSANG@LEG2</t>
+          <t>FSW2_MINR@LEG2</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>FSW2_MINR@LEG2</t>
+          <t>FSW2_THDL@LEG2</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>FSW2_THDL@LEG2</t>
+          <t>FSW2_RELANG@LEG2</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>FSW2_RELANG@LEG2</t>
+          <t>FSW2_RELR@LEG2</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>FSW2_RELR@LEG2</t>
+          <t>FSW2_STEMR@LEG2</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>FSW2_STEMR@LEG2</t>
+          <t>FSW2_HEADL@LEG2</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>FSW2_HEADL@LEG2</t>
+          <t>NUTHEX2@NUTHEX2</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>NUTHEX2@NUTHEX2</t>
+          <t>DEPTH@NUTCUT2</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>DEPTH@NUTCUT2</t>
+          <t>FSW2_CBR@LEG2</t>
         </is>
       </c>
       <c r="AE1" t="inlineStr">
         <is>
-          <t>FSW2_CBR@LEG2</t>
+          <t>FSW2_CBD@LEG2</t>
         </is>
       </c>
       <c r="AF1" t="inlineStr">
         <is>
-          <t>FSW2_CBD@LEG2</t>
+          <t>D1@BORE1</t>
         </is>
       </c>
       <c r="AG1" t="inlineStr">
         <is>
-          <t>D1@BORE1</t>
+          <t>DEPTH@BORECUT1</t>
         </is>
       </c>
       <c r="AH1" t="inlineStr">
         <is>
-          <t>DEPTH@BORECUT1</t>
+          <t>D2@BORE2</t>
         </is>
       </c>
       <c r="AI1" t="inlineStr">
         <is>
-          <t>D2@BORE2</t>
+          <t>DEPTH@BORECUT2</t>
         </is>
       </c>
       <c r="AJ1" t="inlineStr">
         <is>
-          <t>DEPTH@BORECUT2</t>
+          <t>THDDIA@THD_End1</t>
         </is>
       </c>
       <c r="AK1" t="inlineStr">
         <is>
-          <t>THDDIA@THD_End1</t>
+          <t>THDPITCH@THD_End1</t>
         </is>
       </c>
       <c r="AL1" t="inlineStr">
         <is>
-          <t>THDPITCH@THD_End1</t>
+          <t>DEPTH@THD_End1</t>
         </is>
       </c>
       <c r="AM1" t="inlineStr">
         <is>
-          <t>DEPTH@THD_End1</t>
+          <t>Profile_Height@THD_End1_PROF</t>
         </is>
       </c>
       <c r="AN1" t="inlineStr">
         <is>
-          <t>Profile_Height@THD_End1_PROF</t>
+          <t>Profile_Land@THD_End1_PROF</t>
         </is>
       </c>
       <c r="AO1" t="inlineStr">
         <is>
-          <t>Profile_Land@THD_End1_PROF</t>
+          <t>THDPITCH@THD_End1_PROF</t>
         </is>
       </c>
       <c r="AP1" t="inlineStr">
         <is>
-          <t>THDPITCH@THD_End1_PROF</t>
+          <t>HELIXDIA@HELIXSK_2</t>
         </is>
       </c>
       <c r="AQ1" t="inlineStr">
         <is>
-          <t>HELIXDIA@HELIXSK_2</t>
+          <t>HEIGHT@HELIX_2</t>
         </is>
       </c>
       <c r="AR1" t="inlineStr">
         <is>
-          <t>HEIGHT@HELIX_2</t>
+          <t>PITCH@HELIX_2</t>
         </is>
       </c>
       <c r="AS1" t="inlineStr">
         <is>
-          <t>PITCH@HELIX_2</t>
+          <t>PROF_R@THDPROF_2</t>
         </is>
       </c>
       <c r="AT1" t="inlineStr">
         <is>
-          <t>PROF_R@THDPROF_2</t>
+          <t>APEXR@THDPROF_2</t>
         </is>
       </c>
       <c r="AU1" t="inlineStr">
         <is>
-          <t>APEXR@THDPROF_2</t>
+          <t>PROF_AX@THDPROF_2</t>
         </is>
       </c>
       <c r="AV1" t="inlineStr">
         <is>
-          <t>PROF_AX@THDPROF_2</t>
+          <t>HEXAF@HEX1</t>
         </is>
       </c>
       <c r="AW1" t="inlineStr">
         <is>
-          <t>HEXAF@HEX1</t>
+          <t>HEXL@HEX1_BODY</t>
         </is>
       </c>
       <c r="AX1" t="inlineStr">
         <is>
-          <t>HEXL@HEX1_BODY</t>
+          <t>HEXAF@HEX2</t>
         </is>
       </c>
       <c r="AY1" t="inlineStr">
         <is>
-          <t>HEXAF@HEX2</t>
+          <t>HEXL@HEX2_BODY</t>
         </is>
       </c>
       <c r="AZ1" t="inlineStr">
         <is>
-          <t>HEXL@HEX2_BODY</t>
+          <t>PUCK_HB@PUCK</t>
         </is>
       </c>
       <c r="BA1" t="inlineStr">
         <is>
-          <t>PUCK_HB@PUCK</t>
+          <t>PUCK_HT@PUCK</t>
         </is>
       </c>
       <c r="BB1" t="inlineStr">
         <is>
-          <t>PUCK_HT@PUCK</t>
+          <t>PUCK_R1B@PUCK</t>
         </is>
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>PUCK_R1B@PUCK</t>
+          <t>PUCK_R1T@PUCK</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>PUCK_R1T@PUCK</t>
+          <t>PUCK_XC@PUCK</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>PUCK_XC@PUCK</t>
+          <t>$PRP@PartNo</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>$PRP@PartNo</t>
+          <t>$PRP@Description</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>$PRP@Description</t>
+          <t>$PRP@GeometryRoot</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>$PRP@GeometryRoot</t>
+          <t>$PRP@End1_Thread</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>$PRP@End1_Thread</t>
+          <t>$PRP@End2_Thread</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>$PRP@End2_Thread</t>
+          <t>$PRP@DataStatus</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>$PRP@DataStatus</t>
+          <t>$PRP@AxialSource</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
         <is>
-          <t>$PRP@AxialSource</t>
+          <t>$COMMENT</t>
         </is>
       </c>
       <c r="BM1" t="inlineStr">
-        <is>
-          <t>$COMMENT</t>
-        </is>
-      </c>
-      <c r="BN1" t="inlineStr">
         <is>
           <t>$PRP@OMiSKU</t>
         </is>
@@ -746,440 +741,434 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>FS6500-10-10-FG</t>
+          <t>FS6500-20-20-FG</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.31</v>
+        <v>1.76</v>
       </c>
       <c r="C2" t="n">
-        <v>0.53</v>
+        <v>0.8125</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>0.84375</v>
       </c>
       <c r="E2" t="n">
-        <v>0.555</v>
+        <v>0.62775</v>
       </c>
       <c r="F2" t="n">
         <v>45</v>
       </c>
       <c r="G2" t="n">
-        <v>0.445</v>
+        <v>0.7825</v>
       </c>
       <c r="H2" t="n">
-        <v>0.378</v>
+        <v>0.6585</v>
       </c>
       <c r="I2" t="n">
         <v>0.052</v>
       </c>
       <c r="J2" t="n">
+        <v>0.5565</v>
+      </c>
+      <c r="K2" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.8125</v>
+      </c>
+      <c r="M2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0.7005</v>
+      </c>
+      <c r="O2" t="n">
+        <v>1.095</v>
+      </c>
+      <c r="P2" t="n">
+        <v>0.8655</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1.08253</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.583</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.79864</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.45564</v>
+      </c>
+      <c r="X2" t="n">
+        <v>45</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.7985</v>
+      </c>
+      <c r="AA2" t="n">
         <v>0.276</v>
       </c>
-      <c r="K2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="L2" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="M2" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="N2" t="n">
-        <v>0.4085</v>
-      </c>
-      <c r="O2" t="n">
-        <v>0.953</v>
-      </c>
-      <c r="P2" t="n">
-        <v>0.516</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>0.157</v>
-      </c>
-      <c r="R2" t="n">
-        <v>0.555</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.548</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.65241</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.532</v>
-      </c>
-      <c r="V2" t="n">
-        <v>60</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.46134</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.40591</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>45</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>0.4615</v>
-      </c>
       <c r="AB2" t="n">
-        <v>0.236</v>
+        <v>1.875</v>
       </c>
       <c r="AC2" t="n">
-        <v>1.13</v>
+        <v>0.65</v>
       </c>
       <c r="AD2" t="n">
-        <v>0.548</v>
+        <v>0.854</v>
       </c>
       <c r="AE2" t="n">
-        <v>0.51</v>
+        <v>0.05</v>
       </c>
       <c r="AF2" t="n">
-        <v>0.05</v>
+        <v>1.02</v>
       </c>
       <c r="AG2" t="n">
-        <v>0.49</v>
+        <v>1.76</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.31</v>
+        <v>1.02</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.45</v>
+        <v>2.873</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2.152</v>
+        <v>1.6875</v>
       </c>
       <c r="AK2" t="n">
-        <v>1</v>
+        <v>0.08333</v>
       </c>
       <c r="AL2" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.62775</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.555</v>
+        <v>0.04511</v>
       </c>
       <c r="AN2" t="n">
-        <v>0.03866</v>
+        <v>0.02083</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.01786</v>
+        <v>0.08333</v>
       </c>
       <c r="AP2" t="n">
-        <v>0.07142999999999999</v>
+        <v>1.59728</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.9226799999999999</v>
+        <v>0.5376</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.484</v>
+        <v>0.08333</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.07142999999999999</v>
+        <v>0.79864</v>
       </c>
       <c r="AT2" t="n">
-        <v>0.46134</v>
+        <v>0.84375</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.5</v>
+        <v>2.873</v>
       </c>
       <c r="AV2" t="n">
-        <v>2.152</v>
+        <v>1.625</v>
       </c>
       <c r="AW2" t="n">
-        <v>1.06</v>
+        <v>1.071</v>
       </c>
       <c r="AX2" t="n">
-        <v>0.7</v>
+        <v>1.625</v>
       </c>
       <c r="AY2" t="n">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.64</v>
+        <v>0.8125</v>
       </c>
       <c r="BA2" t="n">
-        <v>0.53</v>
+        <v>0.8125</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.53</v>
+        <v>0.4686</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.3055</v>
+        <v>0.4686</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.3055</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>0.61149</v>
+        <v>0.93769</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>FS6500-20-20-FG</t>
+        </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>FS6500-10-10-FG</t>
+          <t>ORFS 90 deg Male Face Seal x Female Face Seal Swivel Elbow - swivel nut mouth counterbored (-10 up), 1 11/16-12 UN (male O-ring face seal, SAE J1453) x 1 11/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>ORFS 90 deg Male Face Seal x Female Face Seal Swivel Elbow - swivel nut mouth counterbored (-10 up), 1-14 UN (male O-ring face seal, SAE J1453) x 1-14 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>FS6500C</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>FS6500C</t>
+          <t>1 11/16-12 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>1-14 UN (male O-ring face seal, SAE J1453)</t>
+          <t>1 11/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>1-14 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L7@DRIVE: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-20-20-FG col "M LGTH" = "1.76" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 280.7, page verified True) [Brennan = yes 2026-10-18] - FS leg face -&gt; crossing; mapping: same-table check: 5/5 rows with an Air-Way value agree to rounding; L21@DRIVE: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-20-20-FG col "AAA LGTH" = "2.29" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 280.7, page verified True) [Brennan = yes 2026-10-18] - swivel leg crossing -&gt; nut face; mapping: same-table check: 5/5 rows with an Air-Way value agree to rounding; SHEX@HEX: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-20-20-FG col "C HEX" = "1.875" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 280.7, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex; mapping: same-table check: 5/5 rows with an Air-Way value agree to rounding; Q-FS-NUT: = Air-Way FF318-20 S 1.88 to rounding; S2HEX@HEX: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-20-20-FG col "JJ FLATS" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 280.7, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 5/5 rows with an Air-Way value agree to rounding; THDMAJ_D_1@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -20 = 1.6875 (PLAN.md s2 FS_THR / the -20 thread of every staged ORFS row); = Brennan "A THREAD" "1-11/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_D_2@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -20 = 1.6875 (PLAN.md s2 FS_THR / the -20 thread of every staged ORFS row); = Brennan "B THREAD" "1-11/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D_1: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-20-20-FG col "A THREAD" "1-11/16-12" in the table's format; $PRP@Thread_D_2: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-20-20-FG col "B THREAD" "1-11/16-12" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6500: FSM -20 bore on 2 Air-Way row(s): 1.02 (unanimous) [Air-Way, not Brennan]; D19@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: forged ORFS tables: FSSW -20 bore on 3 Air-Way row(s) in 2 tables: 1.02 x3 (unanimous) [Air-Way, not Brennan] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>Air-Way FF6500 (s24, double-pass 2026-10-15, parts.air-way.com/api/series/24, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p9 FS6500-10-10-FG (ORFS-p009-t01); FORGED part: Air-Way NON-forged row FF6500-10-10-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); each leg bore runs from its face to the axis crossing</t>
+          <t>forged (-FG): Air-Way non-forged row differs from Brennan forged on JJ FLATS=1.625 vs Air-Way S2=1.61 - stays MISSING (user 2026-10-15) | forged (-FG): the Air-Way NON-forged series FF6500 is used only where Brennan FS6500-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5583 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p9 FS6500-20-20-FG ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library)</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>forged (-FG): Air-Way non-forged FF6500-10-10-O = Brennan forged FS6500-10-10-FG p9 on every compared cell (M LGTH ~ L7, AAA LGTH ~ L21, C HEX ~ S, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6500 is used only where Brennan FS6500-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5580 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs) | leg 2 hex arm 0.640 barely clears the corner puck (radius 0.612)</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>FS6500-10-10-FG</t>
+          <t>FS6500-20-20-FG</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>FS6500-20-20-FG</t>
+          <t>FS6500-10-10-FG</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1.76</v>
+        <v>1.31</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8125</v>
+        <v>0.53</v>
       </c>
       <c r="D3" t="n">
-        <v>0.84375</v>
+        <v>0.5</v>
       </c>
       <c r="E3" t="n">
-        <v>0.62775</v>
+        <v>0.555</v>
       </c>
       <c r="F3" t="n">
         <v>45</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7825</v>
+        <v>0.445</v>
       </c>
       <c r="H3" t="n">
-        <v>0.6585</v>
+        <v>0.378</v>
       </c>
       <c r="I3" t="n">
         <v>0.052</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5565</v>
+        <v>0.276</v>
       </c>
       <c r="K3" t="n">
-        <v>2.29</v>
+        <v>1.62</v>
       </c>
       <c r="L3" t="n">
-        <v>0.8125</v>
+        <v>0.53</v>
       </c>
       <c r="M3" t="n">
-        <v>1.2</v>
+        <v>0.98</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7005</v>
+        <v>0.4085</v>
       </c>
       <c r="O3" t="n">
-        <v>1.095</v>
+        <v>0.953</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8655</v>
+        <v>0.516</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.2</v>
+        <v>0.157</v>
       </c>
       <c r="R3" t="n">
-        <v>0.93</v>
+        <v>0.555</v>
       </c>
       <c r="S3" t="n">
-        <v>0.65</v>
+        <v>0.548</v>
       </c>
       <c r="T3" t="n">
-        <v>1.08253</v>
+        <v>0.65241</v>
       </c>
       <c r="U3" t="n">
-        <v>0.583</v>
+        <v>0.532</v>
       </c>
       <c r="V3" t="n">
-        <v>60</v>
+        <v>0.46134</v>
       </c>
       <c r="W3" t="n">
-        <v>0.79864</v>
+        <v>0.42121</v>
       </c>
       <c r="X3" t="n">
-        <v>0.45564</v>
+        <v>45</v>
       </c>
       <c r="Y3" t="n">
-        <v>45</v>
+        <v>0.51</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.86</v>
+        <v>0.4615</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.7985</v>
+        <v>0.236</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.276</v>
+        <v>1.13</v>
       </c>
       <c r="AC3" t="n">
-        <v>1.875</v>
+        <v>0.548</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.65</v>
+        <v>0.51</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.854</v>
+        <v>0.05</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.05</v>
+        <v>0.49</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.02</v>
+        <v>1.31</v>
       </c>
       <c r="AH3" t="n">
-        <v>1.76</v>
+        <v>0.45</v>
       </c>
       <c r="AI3" t="n">
-        <v>1.02</v>
+        <v>2.152</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2.873</v>
+        <v>1</v>
       </c>
       <c r="AK3" t="n">
-        <v>1.6875</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.08333</v>
+        <v>0.555</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.62775</v>
+        <v>0.03866</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.04511</v>
+        <v>0.01786</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.02083</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.08333</v>
+        <v>0.9226799999999999</v>
       </c>
       <c r="AQ3" t="n">
-        <v>1.59728</v>
+        <v>0.484</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.5376</v>
+        <v>0.07142999999999999</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.08333</v>
+        <v>0.46134</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.79864</v>
+        <v>0.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.84375</v>
+        <v>2.152</v>
       </c>
       <c r="AV3" t="n">
-        <v>2.873</v>
+        <v>1.06</v>
       </c>
       <c r="AW3" t="n">
-        <v>1.625</v>
+        <v>0.7</v>
       </c>
       <c r="AX3" t="n">
-        <v>1.071</v>
+        <v>1.06</v>
       </c>
       <c r="AY3" t="n">
-        <v>1.625</v>
+        <v>0.64</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.09</v>
+        <v>0.53</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.8125</v>
+        <v>0.53</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.8125</v>
+        <v>0.3055</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.4686</v>
+        <v>0.3055</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.4686</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>0.93769</v>
+        <v>0.61149</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>FS6500-10-10-FG</t>
+        </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>FS6500-20-20-FG</t>
+          <t>ORFS 90 deg Male Face Seal x Female Face Seal Swivel Elbow - swivel nut mouth counterbored (-10 up), 1-14 UN (male O-ring face seal, SAE J1453) x 1-14 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>ORFS 90 deg Male Face Seal x Female Face Seal Swivel Elbow - swivel nut mouth counterbored (-10 up), 1 11/16-12 UN (male O-ring face seal, SAE J1453) x 1 11/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>FS6500C</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>FS6500C</t>
+          <t>1-14 UN (male O-ring face seal, SAE J1453)</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>1 11/16-12 UN (male O-ring face seal, SAE J1453)</t>
+          <t>1-14 UN (female O-ring face-seal swivel, SAE J1453)</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>1 11/16-12 UN (female O-ring face-seal swivel, SAE J1453)</t>
+          <t>ASSUMED</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>Air-Way FF6500 (s24, double-pass 2026-10-15, parts.air-way.com/api/series/24, two fetches identical) [user 2026-10-15: "use airway dimensions, check brennan too"]; checked against the Brennan ORFS catalog p9 FS6500-10-10-FG (ORFS-p009-t01); FORGED part: Air-Way NON-forged row FF6500-10-10-O, used because Brennan's forged row matches every compared cell [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); each leg bore runs from its face to the axis crossing</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>[BRENNAN-ONLY 2026-10-18] not built: forged part where Air-Way and Brennan do not match on every cell (user 2026-10-15: the rest stay MISSING) -&gt; 2026-10-18 Brennan allowed (user: "yes use brennan but still differentiate"): L7@DRIVE: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-20-20-FG col "M LGTH" = "1.76" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 280.7, page verified True) [Brennan = yes 2026-10-18] - FS leg face -&gt; crossing; mapping: same-table check: 5/5 rows with an Air-Way value agree to rounding; L21@DRIVE: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-20-20-FG col "AAA LGTH" = "2.29" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 280.7, page verified True) [Brennan = yes 2026-10-18] - swivel leg crossing -&gt; nut face; mapping: same-table check: 5/5 rows with an Air-Way value agree to rounding; SHEX@HEX: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-20-20-FG col "C HEX" = "1.875" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 280.7, page verified True) [Brennan = yes 2026-10-18] - swivel nut hex; mapping: same-table check: 5/5 rows with an Air-Way value agree to rounding; Q-FS-NUT: = Air-Way FF318-20 S 1.88 to rounding; S2HEX@HEX: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-20-20-FG col "JJ FLATS" = "1.625" (07_RAW_EXTRACTS/brennan_catalogs/ORFS Catalog.pdf; tools/_out/brennan_catalog_20261001/catalog_verified.json, line_y 280.7, page verified True) [Brennan = yes 2026-10-18] - forged flats; mapping: same-table check: 5/5 rows with an Air-Way value agree to rounding; THDMAJ_D_1@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -20 = 1.6875 (PLAN.md s2 FS_THR / the -20 thread of every staged ORFS row); = Brennan "A THREAD" "1-11/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; THDMAJ_D_2@DRIVE: end library: face-seal (SAE J1453) thread FS_THR of dash -20 = 1.6875 (PLAN.md s2 FS_THR / the -20 thread of every staged ORFS row); = Brennan "B THREAD" "1-11/16-12" of this row [Q-TRANSFER-ENDLIB yes 2026-10-08]; $PRP@Thread_D_1: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-20-20-FG col "A THREAD" "1-11/16-12" in the table's format; $PRP@Thread_D_2: Brennan ORFS catalog p9 table ORFS-p009-t01 "FS6500-FG MFS-FFSS 90 DEG ELBOW" row FS6500-20-20-FG col "B THREAD" "1-11/16-12" in the table's format; D1@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: same table FS6500: FSM -20 bore on 2 Air-Way row(s): 1.02 (unanimous) [Air-Way, not Brennan]; D19@BORE: per-dash transfer, user 2026-10-18 Q-FS-XFER yes: forged ORFS tables: FSSW -20 bore on 3 Air-Way row(s) in 2 tables: 1.02 x3 (unanimous) [Air-Way, not Brennan] | MODEL: forged elbow body per the 2500HX pattern (Brennan 2500-06-06-FG STEP): one hex arm along each leg, A/F = max(Air-Way hex, JIC thread majors), flats normal to Z, 30deg double-cone corner puck about Z (radius = hex corner, height = flats); hex-end 75deg chamfers and edge fillets NOT modelled; face-seal legs (SAE J1453 male face seal): face, rectangular O-ring groove, land, 45deg nose chamfer and end length measured per dash on the male leg of BRENNAN_FS6500-NN-NN-FG (gen_straight2 FSMF_MEAS; -08 also = FS2403-08-08); the thread major runs to the end length, then meets the hex flats of the row with a radial step down (thread above the flats), a step up (flats above the thread; Brennan FS6500-06 / -10, FS2501-08-08-FG) or no step where the flats = the thread major within 0.003 (Brennan FS6500-04 / -12 / -16; masters &lt;root&gt;N); hex A/F = the row S2 (face-seal threads are not in the 2603HX A/F rule, PLAN R1); the 75deg chamfer of the hex arm end and the O-ring are NOT modelled; single manufacturer (Brennan pilots; Air-Way 3D models not yet measured); female face-seal SWIVEL leg (Brennan FS6500-08-08-FG, SAE J1453): leg length = the row L21, crossing -&gt; the stem's flat SEAL face (= Brennan AAA; measured - the nut face is 0.433 further out at -08, PLAN.md had read L21 as the nut face); nut hex = the row SHEX (= FF318 S, Q-FS-NUT) over the measured hex length; rear skirt cone, skirt, nut rear face, neck and body face measured; nut thread = the face-seal thread of the dash, minor = ASME B1.1 basic minor, helical 60deg thread over the measured length, 45deg mouth countersink and 45deg relief, a cone to the stem head, stem head to the seal face (measured, -08 only - other sizes need BRENNAN_FS6500-NN-NN-FG); NOT modelled: nut hex chamfers, the skirt groove, the nut / stem clearance (one solid), the O-ring; single manufacturer (Brennan); each leg bore runs from its face to the axis crossing</t>
+          <t>forged (-FG): Air-Way non-forged FF6500-10-10-O = Brennan forged FS6500-10-10-FG p9 on every compared cell (M LGTH ~ L7, AAA LGTH ~ L21, C HEX ~ S, JJ FLATS ~ S2) [user 2026-10-15: "Yes - use Air-Way's sizes for the 121 forged ORFS parts where Brennan's forged row matches on every cell (VERIFIED); the rest stay MISSING."] | forged (-FG): the Air-Way NON-forged series FF6500 is used only where Brennan FS6500-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5580 (no dimensions) | DataStatus VERIFIED -&gt; ASSUMED: the face-seal end shapes are single-source (Brennan pilot STEPs) | leg 2 hex arm 0.640 barely clears the corner puck (radius 0.612)</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>forged (-FG): Air-Way non-forged row differs from Brennan forged on JJ FLATS=1.625 vs Air-Way S2=1.61 - stays MISSING (user 2026-10-15) | forged (-FG): the Air-Way NON-forged series FF6500 is used only where Brennan FS6500-FG prints the same value in every compared cell (user 2026-10-15); forged body shape from Brennan (shape only) | OMi parts file row 5583 (no dimensions) | 2026-10-18 Brennan = yes (wave 3 ORFS, staged, not shipped): sizes from Brennan ORFS p9 FS6500-20-20-FG ($PRP@DimSource BRENNAN; to undo clear the BRENNAN cells and regenerate); threads by dash (end library)</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>FS6500-20-20-FG</t>
+          <t>FS6500-10-10-FG</t>
         </is>
       </c>
     </row>
